--- a/results/by_outcome/full_results_education_PGI_Sisters.xlsx
+++ b/results/by_outcome/full_results_education_PGI_Sisters.xlsx
@@ -474,32 +474,32 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>0.609367268934911</v>
+        <v>0.626806234764463</v>
       </c>
       <c r="D2" t="n">
-        <v>0.390952398601252</v>
+        <v>0.373499161260008</v>
       </c>
       <c r="E2" t="n">
-        <v>1.00031966753616</v>
+        <v>1.00030539602447</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="n">
-        <v>0.390827463748851</v>
+        <v>0.373385130925427</v>
       </c>
       <c r="K2" t="n">
-        <v>0.354105183303147</v>
+        <v>0.341487633822998</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0282039735379271</v>
+        <v>0.0268986004285425</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0555930559456372</v>
+        <v>0.0549825948947481</v>
       </c>
       <c r="N2" t="n">
-        <v>0.382309156841074</v>
+        <v>0.368386234251541</v>
       </c>
       <c r="O2"/>
     </row>
@@ -514,10 +514,10 @@
       <c r="D3"/>
       <c r="E3"/>
       <c r="F3" t="n">
-        <v>0.58196943112671</v>
+        <v>0.598713663557996</v>
       </c>
       <c r="G3" t="n">
-        <v>0.354218379234636</v>
+        <v>0.341591922788774</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
@@ -541,10 +541,10 @@
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" t="n">
-        <v>0.553756441694052</v>
+        <v>0.571806848403819</v>
       </c>
       <c r="I4" t="n">
-        <v>0.35069132639285</v>
+        <v>0.339568155527287</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
@@ -552,7 +552,7 @@
       <c r="M4"/>
       <c r="N4"/>
       <c r="O4" t="n">
-        <v>0.446420519694488</v>
+        <v>0.428367725820175</v>
       </c>
     </row>
   </sheetData>
@@ -597,13 +597,13 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.390827463748851</v>
+        <v>0.373385130925427</v>
       </c>
       <c r="D2" t="n">
-        <v>0.332434520381357</v>
+        <v>0.31553040074819</v>
       </c>
       <c r="E2" t="n">
-        <v>0.443640323854374</v>
+        <v>0.421672514898084</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -620,13 +620,13 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.382309156841074</v>
+        <v>0.368386234251541</v>
       </c>
       <c r="D3" t="n">
-        <v>0.284528260669492</v>
+        <v>0.275861535333301</v>
       </c>
       <c r="E3" t="n">
-        <v>0.460520844737996</v>
+        <v>0.4350929608692</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.446420519694488</v>
+        <v>0.428367725820175</v>
       </c>
       <c r="D4" t="n">
-        <v>0.350023713226597</v>
+        <v>0.33426961001896</v>
       </c>
       <c r="E4" t="n">
-        <v>0.521739515082352</v>
+        <v>0.488367038833314</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -666,16 +666,16 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0641113628534141</v>
+        <v>0.0599814915686344</v>
       </c>
       <c r="D5" t="n">
-        <v>0.033646577700619</v>
+        <v>0.0386150021127891</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0925075852165024</v>
+        <v>0.0839773860924948</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0000100030976136756</v>
+        <v>0.000000230075095974946</v>
       </c>
       <c r="G5" t="n">
         <v>1224</v>

--- a/results/by_outcome/full_results_education_PGI_Sisters.xlsx
+++ b/results/by_outcome/full_results_education_PGI_Sisters.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve">Outcome</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t xml:space="preserve">Estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">Lower</t>
@@ -588,6 +591,9 @@
       <c r="G1" t="s">
         <v>24</v>
       </c>
+      <c r="H1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -600,15 +606,18 @@
         <v>0.373385130925427</v>
       </c>
       <c r="D2" t="n">
-        <v>0.31553040074819</v>
+        <v>0.0282299954162664</v>
       </c>
       <c r="E2" t="n">
-        <v>0.421672514898084</v>
+        <v>0.31847270176792</v>
       </c>
       <c r="F2" t="n">
+        <v>0.421820013562484</v>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1224</v>
       </c>
     </row>
@@ -623,15 +632,18 @@
         <v>0.368386234251541</v>
       </c>
       <c r="D3" t="n">
-        <v>0.275861535333301</v>
+        <v>0.0367139176180211</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4350929608692</v>
+        <v>0.281789402402391</v>
       </c>
       <c r="F3" t="n">
+        <v>0.430997240981112</v>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>1224</v>
       </c>
     </row>
@@ -646,21 +658,24 @@
         <v>0.428367725820175</v>
       </c>
       <c r="D4" t="n">
-        <v>0.33426961001896</v>
+        <v>0.0388251207293973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.488367038833314</v>
+        <v>0.34353831932543</v>
       </c>
       <c r="F4" t="n">
+        <v>0.487629833889306</v>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>1224</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -669,15 +684,18 @@
         <v>0.0599814915686344</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0386150021127891</v>
+        <v>0.0135772288417123</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0839773860924948</v>
+        <v>0.0357880231044112</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000000230075095974946</v>
+        <v>0.0845234298710623</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>1224</v>
       </c>
     </row>

--- a/results/by_outcome/full_results_education_PGI_Sisters.xlsx
+++ b/results/by_outcome/full_results_education_PGI_Sisters.xlsx
@@ -606,13 +606,13 @@
         <v>0.373385130925427</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0282299954162664</v>
+        <v>0.0300083285045458</v>
       </c>
       <c r="E2" t="n">
-        <v>0.31847270176792</v>
+        <v>0.311447623064771</v>
       </c>
       <c r="F2" t="n">
-        <v>0.421820013562484</v>
+        <v>0.43046623932585</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -632,13 +632,13 @@
         <v>0.368386234251541</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0367139176180211</v>
+        <v>0.0439521594915725</v>
       </c>
       <c r="E3" t="n">
-        <v>0.281789402402391</v>
+        <v>0.27213141546739</v>
       </c>
       <c r="F3" t="n">
-        <v>0.430997240981112</v>
+        <v>0.443907065482882</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -658,13 +658,13 @@
         <v>0.428367725820175</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0388251207293973</v>
+        <v>0.0445510368698399</v>
       </c>
       <c r="E4" t="n">
-        <v>0.34353831932543</v>
+        <v>0.33386314066962</v>
       </c>
       <c r="F4" t="n">
-        <v>0.487629833889306</v>
+        <v>0.502880613818011</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -684,16 +684,16 @@
         <v>0.0599814915686344</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0135772288417123</v>
+        <v>0.0144906578967959</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0357880231044112</v>
+        <v>0.031166745787456</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0845234298710623</v>
+        <v>0.088047410385277</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.000017416726524333</v>
       </c>
       <c r="H5" t="n">
         <v>1224</v>

--- a/results/by_outcome/full_results_education_PGI_Sisters.xlsx
+++ b/results/by_outcome/full_results_education_PGI_Sisters.xlsx
@@ -493,16 +493,16 @@
         <v>0.373385130925427</v>
       </c>
       <c r="K2" t="n">
-        <v>0.341487633822998</v>
+        <v>0.337786072703765</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0268986004285425</v>
+        <v>0.0249988922016004</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0549825948947481</v>
+        <v>0.0576876322334357</v>
       </c>
       <c r="N2" t="n">
-        <v>0.368386234251541</v>
+        <v>0.362784964905366</v>
       </c>
       <c r="O2"/>
     </row>
@@ -517,10 +517,10 @@
       <c r="D3"/>
       <c r="E3"/>
       <c r="F3" t="n">
-        <v>0.598713663557996</v>
+        <v>0.594107511721377</v>
       </c>
       <c r="G3" t="n">
-        <v>0.341591922788774</v>
+        <v>0.337889231227491</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
@@ -544,10 +544,10 @@
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" t="n">
-        <v>0.571806848403819</v>
+        <v>0.569100984957482</v>
       </c>
       <c r="I4" t="n">
-        <v>0.339568155527287</v>
+        <v>0.32841231035311</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
@@ -555,7 +555,7 @@
       <c r="M4"/>
       <c r="N4"/>
       <c r="O4" t="n">
-        <v>0.428367725820175</v>
+        <v>0.431072763158863</v>
       </c>
     </row>
   </sheetData>
@@ -606,13 +606,13 @@
         <v>0.373385130925427</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0300083285045458</v>
+        <v>0.0298341245092436</v>
       </c>
       <c r="E2" t="n">
-        <v>0.311447623064771</v>
+        <v>0.314720112878704</v>
       </c>
       <c r="F2" t="n">
-        <v>0.43046623932585</v>
+        <v>0.433221518415158</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -629,16 +629,16 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.368386234251541</v>
+        <v>0.362784964905366</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0439521594915725</v>
+        <v>0.0378361677578052</v>
       </c>
       <c r="E3" t="n">
-        <v>0.27213141546739</v>
+        <v>0.28064562729631</v>
       </c>
       <c r="F3" t="n">
-        <v>0.443907065482882</v>
+        <v>0.429970016532681</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -655,16 +655,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.428367725820175</v>
+        <v>0.431072763158863</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0445510368698399</v>
+        <v>0.037579074345992</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33386314066962</v>
+        <v>0.347391141928798</v>
       </c>
       <c r="F4" t="n">
-        <v>0.502880613818011</v>
+        <v>0.495743365559916</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -681,19 +681,19 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0599814915686344</v>
+        <v>0.0682877982534971</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0144906578967959</v>
+        <v>0.0138281098545157</v>
       </c>
       <c r="E5" t="n">
-        <v>0.031166745787456</v>
+        <v>0.0410869969327367</v>
       </c>
       <c r="F5" t="n">
-        <v>0.088047410385277</v>
+        <v>0.092947789243768</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000017416726524333</v>
+        <v>0.00000039396795659119</v>
       </c>
       <c r="H5" t="n">
         <v>1224</v>

--- a/results/by_outcome/full_results_education_PGI_Sisters.xlsx
+++ b/results/by_outcome/full_results_education_PGI_Sisters.xlsx
@@ -493,16 +493,16 @@
         <v>0.373385130925427</v>
       </c>
       <c r="K2" t="n">
-        <v>0.337786072703765</v>
+        <v>0.33190970366237</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0249988922016004</v>
+        <v>0.00315334997829348</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0576876322334357</v>
+        <v>0.0286063218138571</v>
       </c>
       <c r="N2" t="n">
-        <v>0.362784964905366</v>
+        <v>0.335063053640663</v>
       </c>
       <c r="O2"/>
     </row>
@@ -517,10 +517,10 @@
       <c r="D3"/>
       <c r="E3"/>
       <c r="F3" t="n">
-        <v>0.594107511721377</v>
+        <v>0.60134548969249</v>
       </c>
       <c r="G3" t="n">
-        <v>0.337889231227491</v>
+        <v>0.332011067566352</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
@@ -544,10 +544,10 @@
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" t="n">
-        <v>0.569100984957482</v>
+        <v>0.598191176693649</v>
       </c>
       <c r="I4" t="n">
-        <v>0.32841231035311</v>
+        <v>0.288359934824256</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
@@ -555,7 +555,7 @@
       <c r="M4"/>
       <c r="N4"/>
       <c r="O4" t="n">
-        <v>0.431072763158863</v>
+        <v>0.401991452739284</v>
       </c>
     </row>
   </sheetData>
@@ -606,13 +606,13 @@
         <v>0.373385130925427</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0298341245092436</v>
+        <v>0.0272551488395376</v>
       </c>
       <c r="E2" t="n">
-        <v>0.314720112878704</v>
+        <v>0.32162989519559</v>
       </c>
       <c r="F2" t="n">
-        <v>0.433221518415158</v>
+        <v>0.424610923716692</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -629,16 +629,16 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.362784964905366</v>
+        <v>0.335063053640663</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0378361677578052</v>
+        <v>0.0271931404877736</v>
       </c>
       <c r="E3" t="n">
-        <v>0.28064562729631</v>
+        <v>0.276591052842439</v>
       </c>
       <c r="F3" t="n">
-        <v>0.429970016532681</v>
+        <v>0.385575058234413</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -655,16 +655,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.431072763158863</v>
+        <v>0.401991452739284</v>
       </c>
       <c r="D4" t="n">
-        <v>0.037579074345992</v>
+        <v>0.0266947259462357</v>
       </c>
       <c r="E4" t="n">
-        <v>0.347391141928798</v>
+        <v>0.347668834792886</v>
       </c>
       <c r="F4" t="n">
-        <v>0.495743365559916</v>
+        <v>0.453215744639197</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -681,19 +681,19 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0682877982534971</v>
+        <v>0.0669283990986206</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0138281098545157</v>
+        <v>0.0115200206019776</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0410869969327367</v>
+        <v>0.0442891204616556</v>
       </c>
       <c r="F5" t="n">
-        <v>0.092947789243768</v>
+        <v>0.0914384659043263</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00000039396795659119</v>
+        <v>0.00000000312837589167003</v>
       </c>
       <c r="H5" t="n">
         <v>1224</v>
